--- a/data/official_data/knowledge/examinations.xlsx
+++ b/data/official_data/knowledge/examinations.xlsx
@@ -135,14 +135,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,9 +454,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.28515625" customWidth="1"/>
     <col min="6" max="6" width="12.140625" customWidth="1"/>
   </cols>
@@ -460,13 +465,13 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -476,129 +481,129 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="90.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="60.75" x14ac:dyDescent="0.3">
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="90.75" x14ac:dyDescent="0.3">
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="60.75" x14ac:dyDescent="0.3">
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="75.75" x14ac:dyDescent="0.3">
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="75.75" x14ac:dyDescent="0.3">
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="75.75" x14ac:dyDescent="0.3">
+      <c r="D8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="75.75" x14ac:dyDescent="0.3">
+      <c r="D9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>15</v>
       </c>
     </row>
